--- a/src/main/resources/excel/상품_관리_일괄업로드_양식.xlsx
+++ b/src/main/resources/excel/상품_관리_일괄업로드_양식.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GD\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A531CBA-CA8A-484F-8B7E-5F3E22506581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BC6D30-8963-4175-BC06-801A2C4AFCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{43FDC0DC-E506-47B2-9A80-A457FB523B86}"/>
   </bookViews>
@@ -107,9 +107,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SA001</t>
-  </si>
-  <si>
     <t>MT001</t>
   </si>
   <si>
@@ -157,6 +154,10 @@
   </si>
   <si>
     <t>SU001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>US002</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -603,7 +604,7 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D2">
         <v>111</v>
@@ -615,45 +616,45 @@
         <v>111</v>
       </c>
       <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" t="s">
         <v>21</v>
       </c>
-      <c r="H2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2">
+        <v>222</v>
+      </c>
+      <c r="L2">
+        <v>222</v>
+      </c>
+      <c r="M2">
+        <v>222</v>
+      </c>
+      <c r="N2">
+        <v>222</v>
+      </c>
+      <c r="O2">
+        <v>222</v>
+      </c>
+      <c r="P2" t="s">
         <v>23</v>
       </c>
-      <c r="K2">
-        <v>222</v>
-      </c>
-      <c r="L2">
-        <v>222</v>
-      </c>
-      <c r="M2">
-        <v>222</v>
-      </c>
-      <c r="N2">
-        <v>222</v>
-      </c>
-      <c r="O2">
-        <v>222</v>
-      </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" t="s">
-        <v>25</v>
-      </c>
       <c r="R2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>777</v>
@@ -665,21 +666,21 @@
         <v>777</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>111</v>
@@ -691,17 +692,17 @@
         <v>111</v>
       </c>
       <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
         <v>21</v>
       </c>
-      <c r="H4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>22</v>
       </c>
-      <c r="J4" t="s">
-        <v>23</v>
-      </c>
       <c r="K4">
         <v>222</v>
       </c>
@@ -718,13 +719,13 @@
         <v>222</v>
       </c>
       <c r="P4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q4" t="s">
         <v>27</v>
       </c>
-      <c r="Q4" t="s">
-        <v>28</v>
-      </c>
       <c r="R4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/excel/상품_관리_일괄업로드_양식.xlsx
+++ b/src/main/resources/excel/상품_관리_일괄업로드_양식.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GD\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BC6D30-8963-4175-BC06-801A2C4AFCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB50FC17-4A71-438E-909F-1E1692C59442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{43FDC0DC-E506-47B2-9A80-A457FB523B86}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
   <si>
     <t>유류명칭</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -110,9 +110,6 @@
     <t>MT001</t>
   </si>
   <si>
-    <t>test@gmail.com</t>
-  </si>
-  <si>
     <t>Y</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -158,6 +155,14 @@
   </si>
   <si>
     <t>US002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SA001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>admin@gmail.com</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -204,8 +209,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -530,7 +538,7 @@
     <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
@@ -604,57 +612,57 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2">
-        <v>111</v>
+        <v>333</v>
       </c>
       <c r="E2">
-        <v>111</v>
+        <v>333</v>
       </c>
       <c r="F2">
-        <v>111</v>
+        <v>333</v>
       </c>
       <c r="G2" t="s">
         <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" t="s">
         <v>21</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2">
+        <v>333</v>
+      </c>
+      <c r="L2">
+        <v>333</v>
+      </c>
+      <c r="M2">
+        <v>333</v>
+      </c>
+      <c r="N2">
+        <v>333</v>
+      </c>
+      <c r="O2">
+        <v>333</v>
+      </c>
+      <c r="P2" t="s">
         <v>22</v>
       </c>
-      <c r="K2">
-        <v>222</v>
-      </c>
-      <c r="L2">
-        <v>222</v>
-      </c>
-      <c r="M2">
-        <v>222</v>
-      </c>
-      <c r="N2">
-        <v>222</v>
-      </c>
-      <c r="O2">
-        <v>222</v>
-      </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>23</v>
       </c>
-      <c r="Q2" t="s">
-        <v>24</v>
-      </c>
       <c r="R2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3">
         <v>777</v>
@@ -665,22 +673,22 @@
       <c r="F3">
         <v>777</v>
       </c>
-      <c r="I3" t="s">
-        <v>21</v>
+      <c r="I3" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="K3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4">
         <v>111</v>
@@ -695,37 +703,37 @@
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s">
         <v>21</v>
       </c>
-      <c r="J4" t="s">
-        <v>22</v>
-      </c>
       <c r="K4">
-        <v>222</v>
+        <v>111</v>
       </c>
       <c r="L4">
-        <v>222</v>
+        <v>111</v>
       </c>
       <c r="M4">
-        <v>222</v>
+        <v>111</v>
       </c>
       <c r="N4">
-        <v>222</v>
+        <v>111</v>
       </c>
       <c r="O4">
-        <v>222</v>
+        <v>111</v>
       </c>
       <c r="P4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q4" t="s">
         <v>26</v>
       </c>
-      <c r="Q4" t="s">
-        <v>27</v>
-      </c>
       <c r="R4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/excel/상품_관리_일괄업로드_양식.xlsx
+++ b/src/main/resources/excel/상품_관리_일괄업로드_양식.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GD\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB50FC17-4A71-438E-909F-1E1692C59442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F8C1C5-77FA-4175-8C07-D40AACB7CB49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{43FDC0DC-E506-47B2-9A80-A457FB523B86}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>유류명칭</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -96,73 +96,6 @@
   </si>
   <si>
     <t>서브이미지명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>엑셀테스트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MD002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MT001</t>
-  </si>
-  <si>
-    <t>Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>엑셀테스트중입니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트고양이.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>엑셀테스트2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>엑셀테스트중입니다.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트고양이2.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>실패경우도테스트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㅇㅇㅇ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트드럼통.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트드럼통2.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SU001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>US002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SA001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>admin@gmail.com</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -209,11 +142,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -530,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D927C06-B396-4DB3-AE46-1380F6B96571}">
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
@@ -604,138 +534,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2">
-        <v>333</v>
-      </c>
-      <c r="E2">
-        <v>333</v>
-      </c>
-      <c r="F2">
-        <v>333</v>
-      </c>
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2">
-        <v>333</v>
-      </c>
-      <c r="L2">
-        <v>333</v>
-      </c>
-      <c r="M2">
-        <v>333</v>
-      </c>
-      <c r="N2">
-        <v>333</v>
-      </c>
-      <c r="O2">
-        <v>333</v>
-      </c>
-      <c r="P2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3">
-        <v>777</v>
-      </c>
-      <c r="E3">
-        <v>777</v>
-      </c>
-      <c r="F3">
-        <v>777</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4">
-        <v>111</v>
-      </c>
-      <c r="E4">
-        <v>111</v>
-      </c>
-      <c r="F4">
-        <v>111</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4">
-        <v>111</v>
-      </c>
-      <c r="L4">
-        <v>111</v>
-      </c>
-      <c r="M4">
-        <v>111</v>
-      </c>
-      <c r="N4">
-        <v>111</v>
-      </c>
-      <c r="O4">
-        <v>111</v>
-      </c>
-      <c r="P4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R4" t="s">
-        <v>30</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
